--- a/results/final_0624_summary/PlantPseAAC_BinaryVector_summary.xlsx
+++ b/results/final_0624_summary/PlantPseAAC_BinaryVector_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:BE15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,80 +456,260 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>example_precision__0.0</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision__0.1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision__0.2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision__0.3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall__0.0</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall__0.1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall__0.2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall__0.3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>f1__0.0</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>f1__0.1</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>f1__0.2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>f1__0.3</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy__0.0</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy__0.1</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy__0.2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy__0.3</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard__0.0</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard__0.1</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard__0.2</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard__0.3</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1__0.0</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1__0.1</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1__0.2</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1__0.3</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision__0.0</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision__0.1</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision__0.2</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision__0.3</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall__0.0</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall__0.1</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall__0.2</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall__0.3</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mfrd__0.0</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mfrd__0.1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>mfrd__0.2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>mfrd__0.3</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1__0.0</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1__0.1</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1__0.2</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1__0.3</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision__0.0</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision__0.1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision__0.2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision__0.3</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall__0.0</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall__0.1</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall__0.2</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall__0.3</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>subset0_1__0.0</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>subset0_1__0.1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>subset0_1__0.2</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>subset0_1__0.3</t>
         </is>
@@ -563,80 +743,260 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>0.1079±0.0060</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.0974±0.0059</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0933±0.0029</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.0936±0.0016</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.9320±0.0244</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.9550±0.0203</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.9521±0.0166</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.9522±0.0162</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>0.1807±0.0065</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>0.1733±0.0060</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>0.1683±0.0036</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>0.1692±0.0027</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>0.1658±0.0140</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>0.1543±0.0184</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>0.1498±0.0176</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>0.1594±0.0086</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.1079±0.0060</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.0974±0.0058</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.0933±0.0029</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.0935±0.0016</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0.1556±0.0039</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>0.1569±0.0024</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>0.1552±0.0017</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>0.1558±0.0032</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0.0916±0.0022</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>0.0920±0.0015</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0.0909±0.0009</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0.0912±0.0013</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.9169±0.0264</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.9415±0.0263</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.9354±0.0303</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.9344±0.0296</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
         <is>
           <t>0.9424±0.0205</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>0.9667±0.0128</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>0.9720±0.0150</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>0.9592±0.0168</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0.1676±0.0039</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.1689±0.0022</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.1675±0.0018</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.1691±0.0024</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>0.0921±0.0022</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.0926±0.0013</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.0919±0.0011</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.0928±0.0014</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>0.9345±0.0230</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0.9559±0.0202</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0.9517±0.0182</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0.9517±0.0169</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
         <is>
           <t>0.0154±0.0073</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>0.0015±0.0046</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="BD2" t="inlineStr">
         <is>
           <t>0.0005±0.0015</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
@@ -670,80 +1030,260 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>0.1084±0.0066</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.0973±0.0060</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.0933±0.0031</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.0936±0.0016</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.9330±0.0245</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.9550±0.0203</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.9529±0.0168</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.9527±0.0165</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>0.1814±0.0072</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>0.1732±0.0060</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>0.1684±0.0039</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>0.1692±0.0027</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>0.1658±0.0141</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>0.1542±0.0184</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>0.1497±0.0177</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>0.1591±0.0086</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.1084±0.0066</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.0973±0.0059</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.0933±0.0031</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.0934±0.0016</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.1557±0.0040</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0.1569±0.0025</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>0.1553±0.0015</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0.1559±0.0033</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0.0917±0.0023</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0.0920±0.0015</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0.0910±0.0009</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0.0912±0.0014</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.9181±0.0268</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.9415±0.0263</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.9358±0.0299</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.9345±0.0297</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
         <is>
           <t>0.9424±0.0205</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>0.9667±0.0128</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>0.9720±0.0150</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>0.9592±0.0168</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.1678±0.0041</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.1689±0.0022</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.1677±0.0019</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.1691±0.0024</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.0922±0.0023</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.0926±0.0013</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.0919±0.0011</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.0928±0.0014</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>0.9354±0.0232</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.9559±0.0202</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.9526±0.0182</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.9522±0.0173</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
         <is>
           <t>0.0154±0.0073</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>0.0015±0.0046</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="BD3" t="inlineStr">
         <is>
           <t>0.0005±0.0015</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
@@ -777,80 +1317,260 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>0.1079±0.0060</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.0974±0.0059</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.0933±0.0030</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.0935±0.0016</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.9320±0.0244</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.9550±0.0203</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.9526±0.0168</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.9517±0.0159</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>0.1807±0.0065</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>0.1733±0.0060</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>0.1683±0.0039</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>0.1691±0.0027</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>0.1658±0.0140</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>0.1543±0.0184</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>0.1498±0.0177</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>0.1592±0.0086</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.1079±0.0060</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.0974±0.0058</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0.0933±0.0030</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.0934±0.0016</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0.1556±0.0039</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>0.1569±0.0024</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>0.1553±0.0016</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>0.1558±0.0033</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>0.0916±0.0022</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>0.0920±0.0015</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0.0909±0.0009</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0.0912±0.0014</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0.9169±0.0264</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0.9415±0.0263</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>0.9356±0.0300</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>0.9336±0.0291</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
         <is>
           <t>0.9424±0.0205</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>0.9664±0.0129</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>0.9720±0.0150</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
         <is>
           <t>0.9592±0.0168</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>0.1676±0.0039</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0.1689±0.0022</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.1676±0.0020</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0.1690±0.0024</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>0.0921±0.0022</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>0.0926±0.0013</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>0.0919±0.0012</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>0.0928±0.0014</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>0.9345±0.0230</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>0.9559±0.0202</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>0.9522±0.0184</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>0.9513±0.0166</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
         <is>
           <t>0.0154±0.0073</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="BC4" t="inlineStr">
         <is>
           <t>0.0015±0.0046</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="BD4" t="inlineStr">
         <is>
           <t>0.0005±0.0015</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
@@ -884,80 +1604,260 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>0.1084±0.0066</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.0973±0.0060</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.0934±0.0032</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.0935±0.0016</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.9330±0.0245</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.9550±0.0203</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.9539±0.0171</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.9522±0.0162</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>0.1814±0.0072</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>0.1732±0.0060</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>0.1686±0.0042</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>0.1691±0.0027</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>0.1658±0.0141</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>0.1542±0.0184</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>0.1498±0.0177</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>0.1590±0.0086</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0.1084±0.0066</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0.0973±0.0059</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.0934±0.0032</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0.0934±0.0016</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0.1557±0.0040</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>0.1569±0.0025</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>0.1555±0.0016</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>0.1558±0.0034</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>0.0917±0.0023</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>0.0920±0.0015</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0.0911±0.0010</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0.0912±0.0014</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0.9181±0.0268</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0.9415±0.0263</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>0.9364±0.0297</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>0.9338±0.0293</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
         <is>
           <t>0.9424±0.0205</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>0.9664±0.0129</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>0.9720±0.0150</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>0.9592±0.0168</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>0.1678±0.0041</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>0.1689±0.0022</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.1678±0.0022</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0.1691±0.0024</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>0.0922±0.0023</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>0.0926±0.0013</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>0.0920±0.0013</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>0.0928±0.0014</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>0.9354±0.0232</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>0.9559±0.0202</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>0.9536±0.0185</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>0.9517±0.0169</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
         <is>
           <t>0.0154±0.0073</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>0.0015±0.0046</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="BD5" t="inlineStr">
         <is>
           <t>0.0005±0.0015</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
@@ -991,80 +1891,260 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>0.1104±0.0053</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.1052±0.0094</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.1003±0.0066</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.1082±0.0080</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.9386±0.0187</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.9241±0.0327</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.8793±0.0354</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.7989±0.0360</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>0.1835±0.0052</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>0.1799±0.0077</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>0.1749±0.0076</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>0.1861±0.0107</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>0.1685±0.0133</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>0.1809±0.0242</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>0.2173±0.0317</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>0.3450±0.0257</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0.1103±0.0053</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0.1051±0.0094</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0.1001±0.0066</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.1075±0.0078</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0.1572±0.0031</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>0.1569±0.0028</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>0.1545±0.0017</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>0.1559±0.0057</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>0.0926±0.0017</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>0.0925±0.0019</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0.0916±0.0008</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0.0941±0.0028</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0.9250±0.0203</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0.9211±0.0329</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>0.8627±0.0357</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>0.7313±0.0405</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
         <is>
           <t>0.9399±0.0230</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>0.9423±0.0310</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>0.9092±0.0470</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
         <is>
           <t>0.8105±0.0599</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>0.1691±0.0028</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>0.1691±0.0026</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.1680±0.0027</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.1791±0.0071</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>0.0929±0.0016</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>0.0931±0.0014</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>0.0929±0.0016</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>0.1009±0.0043</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>0.9411±0.0173</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>0.9275±0.0313</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>0.8787±0.0345</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>0.7944±0.0357</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
         <is>
           <t>0.0174±0.0070</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="BC6" t="inlineStr">
         <is>
           <t>0.0087±0.0114</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="BD6" t="inlineStr">
         <is>
           <t>0.0026±0.0034</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>0.0015±0.0033</t>
         </is>
@@ -1098,80 +2178,260 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>0.1110±0.0043</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.1052±0.0093</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.1011±0.0072</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.1071±0.0056</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.9356±0.0193</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.9223±0.0306</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.8801±0.0338</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.8041±0.0308</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>0.1842±0.0047</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>0.1801±0.0080</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>0.1764±0.0087</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>0.1859±0.0082</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>0.1709±0.0130</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>0.1834±0.0246</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>0.2227±0.0316</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>0.3471±0.0252</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0.1109±0.0043</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0.1051±0.0093</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0.1009±0.0072</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.1065±0.0056</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>0.1571±0.0032</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>0.1568±0.0026</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>0.1552±0.0016</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0.1567±0.0052</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>0.0926±0.0016</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>0.0925±0.0018</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0.0920±0.0011</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>0.0944±0.0026</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0.9233±0.0229</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>0.9162±0.0323</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>0.8652±0.0380</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>0.7378±0.0377</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
         <is>
           <t>0.9339±0.0183</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>0.9358±0.0312</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>0.9066±0.0388</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>0.8092±0.0690</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>0.1691±0.0028</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0.1693±0.0023</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.1693±0.0032</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.1806±0.0065</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>0.0929±0.0016</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>0.0932±0.0013</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>0.0936±0.0019</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>0.1018±0.0039</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>0.9383±0.0179</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>0.9255±0.0291</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>0.8806±0.0337</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>0.8001±0.0308</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
         <is>
           <t>0.0174±0.0053</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="BC7" t="inlineStr">
         <is>
           <t>0.0077±0.0100</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="BD7" t="inlineStr">
         <is>
           <t>0.0020±0.0034</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>0.0005±0.0015</t>
         </is>
@@ -1205,80 +2465,260 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>0.1105±0.0052</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.1051±0.0093</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.1006±0.0069</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.1075±0.0081</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.9386±0.0186</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.9223±0.0334</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.8793±0.0343</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.7936±0.0375</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>0.1838±0.0050</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>0.1797±0.0076</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>0.1752±0.0079</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>0.1849±0.0108</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>0.1696±0.0135</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>0.1810±0.0239</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>0.2184±0.0320</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>0.3439±0.0258</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0.1105±0.0052</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0.1051±0.0093</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0.1004±0.0069</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0.1068±0.0080</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0.1573±0.0030</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>0.1566±0.0029</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>0.1546±0.0016</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>0.1551±0.0059</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>0.0927±0.0015</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>0.0923±0.0020</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0.0918±0.0008</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0.0937±0.0030</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0.9243±0.0187</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0.9202±0.0332</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>0.8627±0.0352</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>0.7255±0.0393</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
         <is>
           <t>0.9384±0.0222</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>0.9420±0.0288</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>0.9091±0.0447</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>0.8025±0.0619</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>0.1693±0.0026</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>0.1689±0.0028</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.1682±0.0028</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>0.1778±0.0071</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>0.0930±0.0015</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>0.0929±0.0015</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>0.0930±0.0016</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>0.1002±0.0042</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>0.9411±0.0173</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>0.9256±0.0319</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>0.8787±0.0337</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>0.7887±0.0375</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
         <is>
           <t>0.0174±0.0070</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="BC8" t="inlineStr">
         <is>
           <t>0.0087±0.0114</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="BD8" t="inlineStr">
         <is>
           <t>0.0026±0.0034</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="BE8" t="inlineStr">
         <is>
           <t>0.0015±0.0033</t>
         </is>
@@ -1312,80 +2752,260 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>0.1114±0.0051</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.1051±0.0091</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.1011±0.0071</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.1061±0.0055</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.9356±0.0172</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.9238±0.0319</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.8801±0.0334</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.7992±0.0352</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>0.1843±0.0051</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>0.1801±0.0079</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>0.1763±0.0084</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>0.1843±0.0082</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>0.1711±0.0133</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>0.1830±0.0242</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>0.2227±0.0316</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>0.3456±0.0246</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0.1113±0.0051</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0.1050±0.0091</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0.1009±0.0071</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.1055±0.0055</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0.1572±0.0032</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>0.1570±0.0027</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>0.1550±0.0012</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>0.1558±0.0052</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>0.0926±0.0015</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>0.0926±0.0020</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0.0920±0.0009</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>0.0939±0.0025</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0.9226±0.0206</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0.9178±0.0350</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>0.8605±0.0384</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>0.7328±0.0414</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
         <is>
           <t>0.9339±0.0183</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>0.9397±0.0288</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>0.9082±0.0407</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
         <is>
           <t>0.8050±0.0675</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>0.1691±0.0027</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.1694±0.0025</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.1692±0.0028</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.1792±0.0064</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>0.0929±0.0016</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>0.0932±0.0014</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>0.0936±0.0017</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>0.1010±0.0038</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>0.9383±0.0161</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>0.9270±0.0303</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>0.8801±0.0328</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>0.7944±0.0355</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
         <is>
           <t>0.0184±0.0062</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="BC9" t="inlineStr">
         <is>
           <t>0.0077±0.0100</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="BD9" t="inlineStr">
         <is>
           <t>0.0020±0.0034</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>0.0005±0.0015</t>
         </is>
@@ -1424,75 +3044,255 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>0.0491±0.0098</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.0565±0.0157</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.0728±0.0182</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.0491±0.0052</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.0491±0.0103</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0.0581±0.0159</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0.0841±0.0200</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0.0491±0.0052</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>0.0489±0.0098</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>0.0568±0.0155</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>0.0755±0.0185</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>0.9124±0.0010</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>0.9117±0.0018</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>0.9104±0.0014</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>0.8984±0.0033</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0.0491±0.0052</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0.0486±0.0093</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0.0557±0.0151</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0.0710±0.0178</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0.0283±0.0049</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>0.0317±0.0105</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>0.0403±0.0190</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>0.0588±0.0204</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>0.1251±0.0207</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>0.1415±0.0693</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0.1565±0.0682</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>0.1416±0.0639</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0.0164±0.0027</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0.0187±0.0060</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>0.0248±0.0126</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>0.0405±0.0139</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>0.0854±0.0085</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>0.0854±0.0176</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>0.0979±0.0248</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>0.1233±0.0284</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>0.7080±0.1129</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>0.6444±0.1477</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>0.5202±0.0915</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>0.2741±0.0542</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>0.0455±0.0047</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>0.0460±0.0099</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>0.0544±0.0152</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>0.0797±0.0193</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
         <is>
           <t>0.0491±0.0052</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="BC10" t="inlineStr">
         <is>
           <t>0.0476±0.0083</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="BD10" t="inlineStr">
         <is>
           <t>0.0527±0.0142</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="BE10" t="inlineStr">
         <is>
           <t>0.0583±0.0162</t>
         </is>
@@ -1531,75 +3331,255 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>0.0527±0.0159</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.0726±0.0231</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.0947±0.0268</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.0481±0.0151</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.0529±0.0156</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0.0767±0.0232</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0.1088±0.0281</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.0481±0.0151</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>0.0527±0.0157</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>0.0740±0.0230</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>0.0982±0.0266</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>0.9124±0.0022</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>0.9108±0.0017</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>0.9106±0.0024</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>0.8982±0.0019</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0.0481±0.0151</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0.0524±0.0157</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0.0726±0.0231</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>0.0922±0.0257</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>0.0334±0.0162</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>0.0348±0.0190</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>0.0474±0.0191</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>0.0771±0.0350</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>0.1731±0.0523</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>0.1359±0.0876</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>0.1565±0.0839</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>0.1585±0.0752</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>0.0192±0.0095</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>0.0211±0.0112</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>0.0306±0.0129</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>0.0573±0.0258</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="AO11" t="inlineStr">
         <is>
           <t>0.9984±0.0024</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>0.0835±0.0249</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>0.0900±0.0251</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>0.1243±0.0353</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>0.1527±0.0336</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>0.7145±0.1751</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>0.5452±0.1039</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>0.5140±0.0620</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>0.3002±0.0358</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>0.0445±0.0138</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>0.0493±0.0144</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>0.0712±0.0219</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>0.1032±0.0267</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
         <is>
           <t>0.0481±0.0151</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="BC11" t="inlineStr">
         <is>
           <t>0.0517±0.0157</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="BD11" t="inlineStr">
         <is>
           <t>0.0685±0.0237</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>0.0757±0.0240</t>
         </is>
@@ -1653,62 +3633,1103 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>0.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0.0026±0.0034</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0.0061±0.0064</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>0.0138±0.0097</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0.0026±0.0034</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0.0061±0.0064</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>0.0138±0.0097</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
           <t>0.9101±0.0009</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>0.9101±0.0011</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>0.9104±0.0012</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>0.9104±0.0009</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>0.0026±0.0034</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>0.0061±0.0064</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>0.0138±0.0097</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>0.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>0.0014±0.0019</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>0.0037±0.0032</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>0.0113±0.0081</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>0.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>0.0264±0.0343</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>0.0493±0.0349</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>0.0779±0.0498</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>0.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>0.0007±0.0010</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>0.0020±0.0017</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>0.0062±0.0046</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="AO12" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="AP12" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>0.0047±0.0063</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>0.0113±0.0117</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>0.0247±0.0169</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>0.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>0.3167±0.4113</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>0.5417±0.3966</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>0.5933±0.2699</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>0.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>0.0024±0.0032</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>0.0057±0.0060</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>0.0128±0.0089</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>0.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
         <is>
           <t>0.0026±0.0034</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="BD12" t="inlineStr">
         <is>
           <t>0.0061±0.0064</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="BE12" t="inlineStr">
         <is>
           <t>0.0138±0.0097</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ecc</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0.9836±0.0088</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0.9830±0.0062</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0.9784±0.0074</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0.9598±0.0177</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0.0389±0.0158</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.0406±0.0128</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0511±0.0125</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.0637±0.0287</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.0389±0.0158</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0.0409±0.0127</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0.0517±0.0131</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>0.0679±0.0289</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0.0389±0.0158</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0.0407±0.0128</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>0.0512±0.0127</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>0.0643±0.0281</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>0.9116±0.0005</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>0.9117±0.0010</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>0.9114±0.0011</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>0.9066±0.0033</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0.0389±0.0158</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>0.0406±0.0128</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>0.0511±0.0125</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>0.0617±0.0271</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>0.0233±0.0137</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>0.0245±0.0107</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>0.0281±0.0105</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>0.0420±0.0197</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>0.1041±0.0673</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>0.0973±0.0519</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>0.0911±0.0588</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>0.1221±0.0715</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>0.0138±0.0081</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>0.0145±0.0062</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>0.0175±0.0063</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>0.0282±0.0145</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>0.0676±0.0261</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>0.0714±0.0216</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>0.0880±0.0202</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>0.1089±0.0400</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>0.6616±0.1176</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>0.6473±0.1286</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>0.6021±0.0876</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>0.3915±0.0948</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>0.0360±0.0145</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>0.0379±0.0118</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>0.0478±0.0118</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>0.0648±0.0281</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>0.0389±0.0158</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>0.0404±0.0130</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>0.0506±0.0121</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0.0542±0.0255</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>lp</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0.9089±0.0154</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0.8577±0.0319</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.6516±0.0666</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0.3692±0.0357</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0.3640±0.0328</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.2893±0.0289</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.1570±0.0310</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.1129±0.0158</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.3538±0.0331</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0.2853±0.0301</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0.2676±0.0561</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>0.3640±0.0373</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0.3572±0.0329</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0.2844±0.0285</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0.1841±0.0360</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0.1619±0.0187</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>0.8873±0.0061</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0.8761±0.0052</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>0.7997±0.0135</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>0.6703±0.0166</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0.3538±0.0331</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>0.2790±0.0271</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>0.1506±0.0289</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>0.1097±0.0151</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>0.1196±0.0210</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>0.1071±0.0308</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>0.1264±0.0252</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>0.1334±0.0097</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>0.2315±0.0594</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>0.1468±0.0648</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>0.1055±0.0197</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>0.0959±0.0057</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>0.1323±0.0126</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>0.1156±0.0231</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>0.1954±0.0559</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>0.3296±0.0368</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>0.9341±0.0238</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>0.7110±0.0791</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>0.3500±0.0329</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>0.2846±0.0281</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>0.1896±0.0291</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>0.1640±0.0144</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>0.3633±0.0326</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>0.2960±0.0280</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>0.1491±0.0198</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>0.1063±0.0093</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>0.3377±0.0331</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>0.2744±0.0297</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>0.2626±0.0540</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>0.3601±0.0394</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>0.3436±0.0343</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>0.2633±0.0247</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>0.0711±0.0182</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0.0148±0.0117</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>mlknn</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0.8937±0.0213</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0.8782±0.0231</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.8035±0.0380</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0.6876±0.0464</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0.1713±0.0269</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.1690±0.0382</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.1905±0.0332</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0.1660±0.0244</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.1692±0.0219</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0.1774±0.0401</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0.2264±0.0407</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>0.2694±0.0411</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0.1677±0.0235</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0.1693±0.0380</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0.1992±0.0344</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0.1921±0.0271</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>0.9096±0.0046</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0.8994±0.0066</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>0.8780±0.0072</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>0.8243±0.0092</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0.1626±0.0217</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>0.1614±0.0363</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>0.1812±0.0297</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>0.1574±0.0226</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>0.1114±0.0183</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>0.1104±0.0181</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>0.1391±0.0319</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>0.1378±0.0271</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>0.1970±0.0424</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>0.1732±0.0484</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>0.1649±0.0430</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>0.1252±0.0245</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>0.0867±0.0199</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>0.0891±0.0180</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>0.1347±0.0332</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>0.1861±0.0412</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>0.9969±0.0042</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>0.9610±0.0435</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>0.2471±0.0303</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>0.2344±0.0440</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>0.2460±0.0426</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>0.2166±0.0255</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>0.5007±0.0669</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>0.3782±0.0635</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>0.2772±0.0425</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>0.1810±0.0198</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>0.1657±0.0259</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>0.1730±0.0397</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>0.2228±0.0444</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>0.2711±0.0400</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>0.1472±0.0181</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>0.1380±0.0327</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>0.1304±0.0204</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0.0721±0.0201</t>
         </is>
       </c>
     </row>
